--- a/survey_templates/038_intelligent_planning_survey--survey_templates.xlsx
+++ b/survey_templates/038_intelligent_planning_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>planning_process</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>Planning Process</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,22 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Contact Info</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Contact information is optional but will help us better understand your feedback</t>
-        </is>
-      </c>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -570,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>meeting_frequency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Meeting Frequency</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -588,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>planning_process</t>
+          <t>contact_person</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>planning_process</t>
+          <t>Contact Person</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -616,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -634,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Email Address</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,40 +653,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>meeting_availability</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Meeting Availability</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Contact Info</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -708,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Suggestions</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -726,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>communication_channel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Communication Channel</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -749,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>update_frequency</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Update Frequency</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>department_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Department 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -795,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>department_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Department 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -818,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -841,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>planning_process</t>
+          <t>availability</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>planning_process</t>
+          <t>Availability</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -864,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -887,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>contact_info</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -910,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>planning_process</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>planning_process</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>contact_info</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>contact_info</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1102,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1130,68 +965,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>first_page_choices</t>
+          <t>planning_process_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>regularly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Regularly</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>first_page_choices</t>
+          <t>planning_process_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>ad-hoc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Ad-hoc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>planning_process_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>department_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
@@ -1237,70 +1072,70 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>meeting_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>meeting_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>meeting_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>contact_person_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1317,7 +1152,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>contact_person_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1334,170 +1169,204 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>communication_channel_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>communication_channel_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>communication_channel_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>update_frequency_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>update_frequency_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>update_frequency_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>department_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>department_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>it</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>IT</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>contact_info_choices</t>
+          <t>department_3_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>department_3_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>department_3_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>IT</t>
         </is>
       </c>
     </row>
